--- a/diseases/d233/2020-2025.xlsx
+++ b/diseases/d233/2020-2025.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">

--- a/diseases/d233/2020-2025.xlsx
+++ b/diseases/d233/2020-2025.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">

--- a/diseases/d233/2020-2025.xlsx
+++ b/diseases/d233/2020-2025.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>185</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.7186198800324319</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>223</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.8662282878228773</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>228</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.8856504467426728</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>137</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.5321671544023955</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>182</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.7069665846805546</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>179</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.6953132893286773</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>173</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.6720066986249228</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>168</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.6525845397051273</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>183</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.7108510164645138</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>187</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.7263887436003501</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>172</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.6681222668409638</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>193</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.7496953343041046</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>175</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.6742070626657165</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>169</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.6510913919457491</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>225</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.8668376519987783</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>190</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.7319962394656351</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>198</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.7628171337589249</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>212</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.8167536987721823</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>182</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.7011753451723451</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>188</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.7242910158923126</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>164</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.6318283330124429</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>151</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.5817443797858468</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>213</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.8206063105588435</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>152</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.585596991572508</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>153</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.5839475230405942</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>205</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.7824133478648483</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>257</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.9808791726891026</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>199</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.7595134450005113</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>229</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.8740129593221965</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>219</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.8358464545483014</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>208</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.7938632992970169</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>228</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.8701963088448069</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>244</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.931262716483039</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>235</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.8969128621865335</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>232</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.8854629107543649</v>
       </c>
@@ -14625,9 +14520,6 @@
       <c r="O72" t="n">
         <v>208</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.7938632992970169</v>
       </c>
@@ -15021,9 +14913,6 @@
       <c r="O74" t="n">
         <v>235</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.8884310549525229</v>
       </c>
@@ -15417,9 +15306,6 @@
       <c r="O76" t="n">
         <v>239</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.9035532856751191</v>
       </c>
@@ -15813,9 +15699,6 @@
       <c r="O78" t="n">
         <v>244</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.9224560740783644</v>
       </c>
@@ -16209,9 +16092,6 @@
       <c r="O80" t="n">
         <v>188</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.7107448439620184</v>
       </c>
@@ -16605,9 +16485,6 @@
       <c r="O82" t="n">
         <v>244</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.9224560740783644</v>
       </c>
@@ -17001,9 +16878,6 @@
       <c r="O84" t="n">
         <v>240</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.9073338433557683</v>
       </c>
@@ -17397,9 +17271,6 @@
       <c r="O86" t="n">
         <v>226</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.8544060358266817</v>
       </c>
@@ -17793,9 +17664,6 @@
       <c r="O88" t="n">
         <v>257</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.9716033239268017</v>
       </c>
@@ -18189,9 +18057,6 @@
       <c r="O90" t="n">
         <v>214</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.8090393436588934</v>
       </c>
@@ -18585,9 +18450,6 @@
       <c r="O92" t="n">
         <v>238</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.8997727279944702</v>
       </c>
@@ -18981,9 +18843,6 @@
       <c r="O94" t="n">
         <v>272</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>1.028311689136537</v>
       </c>
@@ -19377,9 +19236,6 @@
       <c r="O96" t="n">
         <v>182</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.6880614978781242</v>
       </c>
@@ -19773,9 +19629,6 @@
       <c r="O98" t="n">
         <v>250</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.9358667370688016</v>
       </c>
@@ -20169,9 +20022,6 @@
       <c r="O100" t="n">
         <v>246</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.920892869275701</v>
       </c>
@@ -20565,9 +20415,6 @@
       <c r="O102" t="n">
         <v>265</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.9920187412929299</v>
       </c>
@@ -20961,9 +20808,6 @@
       <c r="O104" t="n">
         <v>236</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.8834581997929488</v>
       </c>
@@ -21357,9 +21201,6 @@
       <c r="O106" t="n">
         <v>301</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>1.126783551430837</v>
       </c>
@@ -21753,9 +21594,6 @@
       <c r="O108" t="n">
         <v>215</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.8048453938791695</v>
       </c>
@@ -22149,9 +21987,6 @@
       <c r="O110" t="n">
         <v>248</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.9283798031722512</v>
       </c>
@@ -22545,9 +22380,6 @@
       <c r="O112" t="n">
         <v>254</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.9508406048619026</v>
       </c>
@@ -22941,9 +22773,6 @@
       <c r="O114" t="n">
         <v>245</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.9171494023274257</v>
       </c>
@@ -23337,9 +23166,6 @@
       <c r="O116" t="n">
         <v>253</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.9470971379136274</v>
       </c>
@@ -23733,9 +23559,6 @@
       <c r="O118" t="n">
         <v>230</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.8609973981032977</v>
       </c>
@@ -24129,9 +23952,6 @@
       <c r="O120" t="n">
         <v>196</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.7337195218619406</v>
       </c>
@@ -24525,9 +24345,6 @@
       <c r="O122" t="n">
         <v>235</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.8712084729213208</v>
       </c>
@@ -24921,9 +24738,6 @@
       <c r="O124" t="n">
         <v>254</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.9416466047745339</v>
       </c>
@@ -25317,9 +25131,6 @@
       <c r="O126" t="n">
         <v>229</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.8489648523360955</v>
       </c>
@@ -25713,9 +25524,6 @@
       <c r="O128" t="n">
         <v>242</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.8971593636040834</v>
       </c>
@@ -26109,9 +25917,6 @@
       <c r="O130" t="n">
         <v>244</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.9045739037991585</v>
       </c>
@@ -26505,9 +26310,6 @@
       <c r="O132" t="n">
         <v>229</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.8489648523360955</v>
       </c>
@@ -26901,9 +26703,6 @@
       <c r="O134" t="n">
         <v>252</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.9342320645794587</v>
       </c>
@@ -27297,9 +27096,6 @@
       <c r="O136" t="n">
         <v>260</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.9638902253597591</v>
       </c>
@@ -27693,9 +27489,6 @@
       <c r="O138" t="n">
         <v>258</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.956475685164684</v>
       </c>
@@ -28089,9 +27882,6 @@
       <c r="O140" t="n">
         <v>246</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.9119884439942335</v>
       </c>
@@ -28485,9 +28275,6 @@
       <c r="O142" t="n">
         <v>215</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.7970630709705699</v>
       </c>
@@ -28880,9 +28667,6 @@
       </c>
       <c r="O144" t="n">
         <v>175</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>0</v>
       </c>
       <c r="R144" t="n">
         <v>0.6487722670690685</v>

--- a/diseases/d233/2020-2025.xlsx
+++ b/diseases/d233/2020-2025.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20661,7 +20661,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22233,7 +22233,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23805,7 +23805,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24198,7 +24198,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26163,7 +26163,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26556,7 +26556,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27342,7 +27342,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27735,7 +27735,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28128,7 +28128,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28521,7 +28521,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN145" t="b">

--- a/diseases/d233/2020-2025.xlsx
+++ b/diseases/d233/2020-2025.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24974,7 +24974,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25367,7 +25367,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25760,7 +25760,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26153,7 +26153,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26546,7 +26546,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26939,7 +26939,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28118,7 +28118,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28511,7 +28511,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28904,7 +28904,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">

--- a/diseases/d233/2020-2025.xlsx
+++ b/diseases/d233/2020-2025.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24974,7 +24974,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25367,7 +25367,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25760,7 +25760,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26153,7 +26153,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26546,7 +26546,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26939,7 +26939,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28118,7 +28118,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28511,7 +28511,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28904,7 +28904,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">

--- a/diseases/d233/2020-2025.xlsx
+++ b/diseases/d233/2020-2025.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24974,7 +24974,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25367,7 +25367,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25760,7 +25760,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26153,7 +26153,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26546,7 +26546,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26939,7 +26939,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28118,7 +28118,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28511,7 +28511,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28904,7 +28904,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">

--- a/diseases/d233/2020-2025.xlsx
+++ b/diseases/d233/2020-2025.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24974,7 +24974,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25367,7 +25367,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25760,7 +25760,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26153,7 +26153,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26546,7 +26546,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26939,7 +26939,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28118,7 +28118,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28511,7 +28511,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28904,7 +28904,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
